--- a/data/raw/genie_civil.xlsx
+++ b/data/raw/genie_civil.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="26" min="1" max="1"/>
@@ -1453,68 +1453,68 @@
         <v>6</v>
       </c>
       <c r="E6" s="47" t="n">
-        <v>15.81</v>
+        <v>11.46</v>
       </c>
       <c r="F6" s="47" t="n">
-        <v>13.72</v>
+        <v>11.53</v>
       </c>
       <c r="G6" s="47" t="n">
-        <v>12.62</v>
+        <v>10.05</v>
       </c>
       <c r="H6" s="46" t="n">
-        <v>10.62</v>
+        <v>8.17</v>
       </c>
       <c r="I6" s="47" t="n">
-        <v>12.31</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J6" s="46" t="n">
-        <v>9.91</v>
+        <v>6.75</v>
       </c>
       <c r="K6" s="47" t="n">
-        <v>13.11</v>
+        <v>8.67</v>
       </c>
       <c r="L6" s="69" t="n">
-        <v>12.81</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="47" t="n">
-        <v>17.43</v>
+        <v>14.35</v>
       </c>
       <c r="O6" s="47" t="n">
-        <v>12.17</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="P6" s="46" t="n">
-        <v>11.44</v>
+        <v>9.06</v>
       </c>
       <c r="Q6" s="47" t="n">
-        <v>15.38</v>
+        <v>10.06</v>
       </c>
       <c r="R6" s="47" t="n">
-        <v>15.77</v>
+        <v>13.31</v>
       </c>
       <c r="S6" s="47" t="n">
-        <v>15.54</v>
+        <v>12.69</v>
       </c>
       <c r="T6" s="47" t="n">
-        <v>14.24</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="U6" s="47" t="n">
-        <v>16.03</v>
+        <v>11</v>
       </c>
       <c r="V6" s="69" t="n">
-        <v>14.69</v>
+        <v>11.21</v>
       </c>
       <c r="W6" s="71" t="n">
-        <v>13.75</v>
+        <v>10.25</v>
       </c>
       <c r="X6" s="64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="81" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -1623,68 +1623,68 @@
         <v>20</v>
       </c>
       <c r="E8" s="46" t="n">
-        <v>10.73</v>
+        <v>7.37</v>
       </c>
       <c r="F8" s="47" t="n">
-        <v>14.99</v>
+        <v>10.66</v>
       </c>
       <c r="G8" s="47" t="n">
-        <v>14.61</v>
+        <v>11.03</v>
       </c>
       <c r="H8" s="47" t="n">
-        <v>13.41</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I8" s="47" t="n">
-        <v>16.53</v>
+        <v>11.71</v>
       </c>
       <c r="J8" s="47" t="n">
-        <v>13.74</v>
+        <v>10.61</v>
       </c>
       <c r="K8" s="47" t="n">
-        <v>16.73</v>
+        <v>11.34</v>
       </c>
       <c r="L8" s="69" t="n">
-        <v>14.24</v>
+        <v>10.37</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="47" t="n">
-        <v>14.49</v>
+        <v>10.27</v>
       </c>
       <c r="O8" s="47" t="n">
-        <v>13.11</v>
+        <v>9.48</v>
       </c>
       <c r="P8" s="47" t="n">
-        <v>13.66</v>
+        <v>10.12</v>
       </c>
       <c r="Q8" s="46" t="n">
-        <v>11.54</v>
+        <v>9.31</v>
       </c>
       <c r="R8" s="47" t="n">
-        <v>19.32</v>
+        <v>13.33</v>
       </c>
       <c r="S8" s="47" t="n">
-        <v>17.08</v>
+        <v>12.86</v>
       </c>
       <c r="T8" s="46" t="n">
-        <v>9.99</v>
+        <v>7.68</v>
       </c>
       <c r="U8" s="47" t="n">
-        <v>12.29</v>
+        <v>8.1</v>
       </c>
       <c r="V8" s="69" t="n">
-        <v>13.89</v>
+        <v>10.14</v>
       </c>
       <c r="W8" s="71" t="n">
-        <v>14.07</v>
+        <v>10.25</v>
       </c>
       <c r="X8" s="64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="81" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -3918,68 +3918,68 @@
         <v>18</v>
       </c>
       <c r="E35" s="46" t="n">
-        <v>9.83</v>
+        <v>7.58</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>12.36</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G35" s="47" t="n">
-        <v>14.01</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H35" s="47" t="n">
-        <v>16.59</v>
+        <v>13.93</v>
       </c>
       <c r="I35" s="47" t="n">
-        <v>14.77</v>
+        <v>12.45</v>
       </c>
       <c r="J35" s="47" t="n">
-        <v>15.44</v>
+        <v>12.53</v>
       </c>
       <c r="K35" s="47" t="n">
-        <v>13.96</v>
+        <v>9.92</v>
       </c>
       <c r="L35" s="69" t="n">
-        <v>13.61</v>
+        <v>10.6</v>
       </c>
       <c r="M35" s="45" t="n">
         <v>8</v>
       </c>
       <c r="N35" s="47" t="n">
-        <v>13.32</v>
+        <v>8.92</v>
       </c>
       <c r="O35" s="46" t="n">
-        <v>10.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P35" s="47" t="n">
-        <v>16.53</v>
+        <v>12.2</v>
       </c>
       <c r="Q35" s="47" t="n">
-        <v>18.52</v>
+        <v>12.49</v>
       </c>
       <c r="R35" s="46" t="n">
-        <v>11.39</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S35" s="47" t="n">
-        <v>12.21</v>
+        <v>8.02</v>
       </c>
       <c r="T35" s="47" t="n">
-        <v>12.32</v>
+        <v>10.25</v>
       </c>
       <c r="U35" s="47" t="n">
-        <v>16.24</v>
+        <v>11.4</v>
       </c>
       <c r="V35" s="69" t="n">
-        <v>13.99</v>
+        <v>10</v>
       </c>
       <c r="W35" s="71" t="n">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="X35" s="64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y35" s="81" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -4344,7 +4343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="26" min="1" max="1"/>
@@ -7387,61 +7386,61 @@
         <v>20</v>
       </c>
       <c r="E37" s="53" t="n">
-        <v>7.61</v>
+        <v>5.95</v>
       </c>
       <c r="F37" s="52" t="n">
-        <v>13.37</v>
+        <v>9.52</v>
       </c>
       <c r="G37" s="52" t="n">
-        <v>18.32</v>
+        <v>13.81</v>
       </c>
       <c r="H37" s="52" t="n">
-        <v>12.54</v>
+        <v>9.52</v>
       </c>
       <c r="I37" s="52" t="n">
-        <v>16.09</v>
+        <v>11.05</v>
       </c>
       <c r="J37" s="52" t="n">
-        <v>17.24</v>
+        <v>14.55</v>
       </c>
       <c r="K37" s="52" t="n">
-        <v>17.19</v>
+        <v>13.84</v>
       </c>
       <c r="L37" s="69" t="n">
-        <v>14.29</v>
+        <v>11.97</v>
       </c>
       <c r="M37" s="45" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="N37" s="52" t="n">
-        <v>15.7</v>
+        <v>9.16</v>
       </c>
       <c r="O37" s="53" t="n">
-        <v>7.85</v>
+        <v>4.44</v>
       </c>
       <c r="P37" s="53" t="n">
-        <v>7.53</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" s="52" t="n">
-        <v>16.49</v>
+        <v>7.55</v>
       </c>
       <c r="R37" s="53" t="n">
-        <v>10.52</v>
+        <v>5.87</v>
       </c>
       <c r="S37" s="52" t="n">
-        <v>18.89</v>
+        <v>10.87</v>
       </c>
       <c r="T37" s="52" t="n">
-        <v>14.85</v>
+        <v>7.46</v>
       </c>
       <c r="U37" s="52" t="n">
-        <v>14.41</v>
+        <v>6.61</v>
       </c>
       <c r="V37" s="69" t="n">
-        <v>12.84</v>
+        <v>8.51</v>
       </c>
       <c r="W37" s="71" t="n">
-        <v>13.56</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="X37" s="64" t="n">
         <v>4</v>
@@ -7472,61 +7471,61 @@
         <v>9</v>
       </c>
       <c r="E38" s="53" t="n">
-        <v>9.4</v>
+        <v>7.25</v>
       </c>
       <c r="F38" s="52" t="n">
-        <v>17.8</v>
+        <v>14.87</v>
       </c>
       <c r="G38" s="52" t="n">
-        <v>17.69</v>
+        <v>13.8</v>
       </c>
       <c r="H38" s="52" t="n">
-        <v>14.69</v>
+        <v>12.24</v>
       </c>
       <c r="I38" s="52" t="n">
-        <v>13.34</v>
+        <v>10.94</v>
       </c>
       <c r="J38" s="52" t="n">
-        <v>12.78</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K38" s="52" t="n">
-        <v>13.93</v>
+        <v>9.32</v>
       </c>
       <c r="L38" s="69" t="n">
-        <v>14.37</v>
+        <v>10.41</v>
       </c>
       <c r="M38" s="45" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="N38" s="52" t="n">
-        <v>12.62</v>
+        <v>7.83</v>
       </c>
       <c r="O38" s="52" t="n">
-        <v>17.12</v>
+        <v>8.84</v>
       </c>
       <c r="P38" s="52" t="n">
-        <v>15.15</v>
+        <v>7.88</v>
       </c>
       <c r="Q38" s="52" t="n">
-        <v>13.12</v>
+        <v>6.9</v>
       </c>
       <c r="R38" s="52" t="n">
-        <v>12.95</v>
+        <v>7.8</v>
       </c>
       <c r="S38" s="53" t="n">
-        <v>11.04</v>
+        <v>6.94</v>
       </c>
       <c r="T38" s="53" t="n">
-        <v>9.06</v>
+        <v>5.67</v>
       </c>
       <c r="U38" s="53" t="n">
-        <v>8.039999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="V38" s="69" t="n">
-        <v>12.62</v>
+        <v>5.97</v>
       </c>
       <c r="W38" s="71" t="n">
-        <v>13.49</v>
+        <v>7.94</v>
       </c>
       <c r="X38" s="64" t="n">
         <v>4</v>
@@ -7557,61 +7556,61 @@
         <v>9</v>
       </c>
       <c r="E39" s="53" t="n">
-        <v>8.16</v>
+        <v>5.68</v>
       </c>
       <c r="F39" s="52" t="n">
-        <v>17.64</v>
+        <v>11.74</v>
       </c>
       <c r="G39" s="52" t="n">
-        <v>19.06</v>
+        <v>13.49</v>
       </c>
       <c r="H39" s="52" t="n">
-        <v>14.53</v>
+        <v>9.91</v>
       </c>
       <c r="I39" s="53" t="n">
-        <v>7.84</v>
+        <v>6.55</v>
       </c>
       <c r="J39" s="53" t="n">
-        <v>10.59</v>
+        <v>8.6</v>
       </c>
       <c r="K39" s="52" t="n">
-        <v>15.3</v>
+        <v>11.88</v>
       </c>
       <c r="L39" s="69" t="n">
-        <v>13.5</v>
+        <v>11.13</v>
       </c>
       <c r="M39" s="45" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="N39" s="52" t="n">
-        <v>19.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O39" s="52" t="n">
-        <v>15.73</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P39" s="52" t="n">
-        <v>13.01</v>
+        <v>7.23</v>
       </c>
       <c r="Q39" s="52" t="n">
-        <v>14.44</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R39" s="52" t="n">
-        <v>18.73</v>
+        <v>10.47</v>
       </c>
       <c r="S39" s="53" t="n">
-        <v>7.6</v>
+        <v>3.89</v>
       </c>
       <c r="T39" s="52" t="n">
-        <v>15.84</v>
+        <v>8.92</v>
       </c>
       <c r="U39" s="52" t="n">
-        <v>17.52</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="V39" s="69" t="n">
-        <v>15.58</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="W39" s="71" t="n">
-        <v>14.54</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="X39" s="64" t="n">
         <v>4</v>
@@ -7622,7 +7621,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
